--- a/lucas/import_data/utility/observation/excel/profiling.xlsx
+++ b/lucas/import_data/utility/observation/excel/profiling.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">depth in cm</t>
   </si>
   <si>
-    <t xml:space="preserve">depth_cm</t>
+    <t xml:space="preserve">depth cm</t>
   </si>
   <si>
     <t xml:space="preserve">Depth in cm</t>
@@ -153,37 +153,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -257,7 +257,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -298,8 +298,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>